--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7272727272727273</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6830985915492958</v>
+        <v>0.6408450704225352</v>
       </c>
       <c r="D2">
-        <v>0.3383458646616541</v>
+        <v>0.3695652173913043</v>
       </c>
       <c r="E2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
